--- a/file/table/TSIG_ProfileLineSplitPointAreaCalculator.xlsx
+++ b/file/table/TSIG_ProfileLineSplitPointAreaCalculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebacorreoescuelaingeduco-my.sharepoint.com/personal/william_aguilar_escuelaing_edu_co/Documents/ECIJG.ClassSourcecode/TSIG/Taller6/Quiz/Q6HA-Admin/ArcGIS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{84A25A9A-671B-446C-9CA8-62F673BEA6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8D8999C-1CE8-42E2-97D1-8682723BA2FB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C81FD2-2D0D-451B-AD49-3FD3B78AB59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A09F916A-28C8-41E1-92D8-E990655A0D79}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{A09F916A-28C8-41E1-92D8-E990655A0D79}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +83,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -107,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -117,6 +123,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1147,9 +1156,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1187,7 +1196,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1293,7 +1302,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1435,7 +1444,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1444,15 +1453,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF81B0C3-12C5-46C7-9D16-31E065C13F8A}">
   <dimension ref="A1:H53"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="5" width="11" style="1"/>
-    <col min="6" max="6" width="13.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.46484375" style="1" customWidth="1"/>
     <col min="8" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
       <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1472,7 +1481,7 @@
         <v>0.11940983666403801</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1498,20 +1507,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A3" s="5">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="5">
         <v>4217</v>
       </c>
       <c r="F3" s="3">
@@ -1522,20 +1531,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
         <v>2</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>2335.4859849999998</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
         <v>4361</v>
       </c>
       <c r="F4" s="3">
@@ -1551,20 +1560,20 @@
         <v>6.1657402752515349E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A5" s="5">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="5">
         <v>3</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <v>4670.9719699999996</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>4430</v>
       </c>
       <c r="F5" s="3">
@@ -1580,20 +1589,20 @@
         <v>2.9544172152246938E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5">
         <v>4</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="5">
         <v>7006.4579549999999</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="5">
         <v>3575</v>
       </c>
       <c r="F6" s="3">
@@ -1609,20 +1618,20 @@
         <v>0.36609082884305977</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="3">
-        <v>5</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
         <v>9341.9439399999992</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="5">
         <v>3414</v>
       </c>
       <c r="F7" s="3">
@@ -1638,20 +1647,20 @@
         <v>6.8936401688576204E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5">
         <v>6</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="5">
         <v>11677.429925</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="5">
         <v>2827</v>
       </c>
       <c r="F8" s="3">
@@ -1667,20 +1676,20 @@
         <v>0.25133955149810061</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A9" s="5">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5">
         <v>7</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>14012.91591</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>1960</v>
       </c>
       <c r="F9" s="3">
@@ -1696,20 +1705,20 @@
         <v>0.37122894573910287</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5">
         <v>8</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="5">
         <v>16348.401895000001</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="5">
         <v>2268</v>
       </c>
       <c r="F10" s="3">
@@ -1725,20 +1734,20 @@
         <v>0.13187833366510218</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5">
         <v>9</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="5">
         <v>18683.887879999998</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="5">
         <v>1823</v>
       </c>
       <c r="F11" s="3">
@@ -1754,20 +1763,20 @@
         <v>0.19053850156159274</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5">
         <v>10</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="5">
         <v>21019.373865000001</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="5">
         <v>1333</v>
       </c>
       <c r="F12" s="3">
@@ -1783,20 +1792,20 @@
         <v>0.20980643992175332</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5">
         <v>11</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="5">
         <v>23354.859850000001</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="5">
         <v>1094</v>
       </c>
       <c r="F13" s="3">
@@ -1812,20 +1821,20 @@
         <v>0.10233416151285535</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="B14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5">
         <v>12</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="5">
         <v>25690.345835</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="5">
         <v>996</v>
       </c>
       <c r="F14" s="3">
@@ -1841,20 +1850,20 @@
         <v>4.1961287984350726E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A15" s="5">
         <v>12</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5">
         <v>13</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="5">
         <v>28025.831819999999</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="5">
         <v>857</v>
       </c>
       <c r="F15" s="3">
@@ -1870,20 +1879,20 @@
         <v>5.951652071249746E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A16" s="5">
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5">
         <v>14</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="5">
         <v>30361.317804999999</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="5">
         <v>833</v>
       </c>
       <c r="F16" s="3">
@@ -1899,20 +1908,20 @@
         <v>1.0276233792085893E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A17" s="5">
         <v>14</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5">
         <v>15</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="5">
         <v>32696.803790000002</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="5">
         <v>630</v>
       </c>
       <c r="F17" s="3">
@@ -1928,20 +1937,20 @@
         <v>8.6919810824726371E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A18" s="5">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5">
         <v>16</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="5">
         <v>35032.289774999997</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="5">
         <v>881</v>
       </c>
       <c r="F18" s="3">
@@ -1957,20 +1966,20 @@
         <v>0.10747227840889846</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A19" s="5">
         <v>16</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="B19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="5">
         <v>17</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="5">
         <v>37367.775759999997</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="5">
         <v>1102</v>
       </c>
       <c r="F19" s="3">
@@ -1986,20 +1995,20 @@
         <v>9.4626986168790936E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A20" s="5">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="5">
         <v>18</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="5">
         <v>39703.261745000003</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="5">
         <v>797</v>
       </c>
       <c r="F20" s="3">
@@ -2015,20 +2024,20 @@
         <v>0.13059380444109114</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A21" s="5">
         <v>18</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="3">
+      <c r="B21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="5">
         <v>19</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="5">
         <v>42038.747730000003</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="5">
         <v>458</v>
       </c>
       <c r="F21" s="3">
@@ -2044,20 +2053,20 @@
         <v>0.14515180231321323</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A22" s="5">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="3">
+      <c r="B22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="5">
         <v>20</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="5">
         <v>44374.233715000002</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="5">
         <v>950</v>
       </c>
       <c r="F22" s="3">
@@ -2073,20 +2082,20 @@
         <v>0.21066279273776081</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A23" s="5">
         <v>20</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3">
+      <c r="B23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="5">
         <v>21</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="5">
         <v>46709.719700000001</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="5">
         <v>419</v>
       </c>
       <c r="F23" s="3">
@@ -2102,20 +2111,20 @@
         <v>0.22736167264990037</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A24" s="5">
         <v>21</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="B24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="5">
         <v>22</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="5">
         <v>49045.205685000001</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="5">
         <v>176</v>
       </c>
       <c r="F24" s="3">
@@ -2131,20 +2140,20 @@
         <v>0.10404686714486966</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A25" s="5">
         <v>22</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="3">
+      <c r="B25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="5">
         <v>23</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="5">
         <v>51380.69167</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="5">
         <v>145</v>
       </c>
       <c r="F25" s="3">
@@ -2160,20 +2169,20 @@
         <v>1.3273468648110945E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A26" s="5">
         <v>23</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="B26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="5">
         <v>24</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="5">
         <v>53716.177655</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="5">
         <v>139</v>
       </c>
       <c r="F26" s="3">
@@ -2189,20 +2198,20 @@
         <v>2.5690584480214732E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A27" s="5">
         <v>24</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
+      <c r="B27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="5">
         <v>25</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="5">
         <v>56051.663639999999</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="5">
         <v>130</v>
       </c>
       <c r="F27" s="3">
@@ -2218,20 +2227,20 @@
         <v>3.8535876720322097E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A28" s="5">
         <v>25</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
+      <c r="B28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5">
         <v>26</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="5">
         <v>58387.149624999998</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="5">
         <v>114</v>
       </c>
       <c r="F28" s="3">
@@ -2247,20 +2256,20 @@
         <v>6.8508225280572623E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A29" s="5">
         <v>26</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="B29" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="5">
         <v>27</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="5">
         <v>60722.635609999998</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="5">
         <v>104</v>
       </c>
       <c r="F29" s="3">
@@ -2276,20 +2285,20 @@
         <v>4.2817640800357883E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A30" s="5">
         <v>27</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="3">
+      <c r="B30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="5">
         <v>28</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="5">
         <v>63058.121594999997</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="5">
         <v>105</v>
       </c>
       <c r="F30" s="3">
@@ -2305,20 +2314,20 @@
         <v>4.2817640800357889E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A31" s="5">
         <v>28</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="3">
+      <c r="B31" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="5">
         <v>29</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="5">
         <v>65393.607580000004</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="5">
         <v>105</v>
       </c>
       <c r="F31" s="3">
@@ -2334,20 +2343,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A32" s="5">
         <v>29</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="3">
+      <c r="B32" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5">
         <v>30</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="5">
         <v>67729.093565000003</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="5">
         <v>104</v>
       </c>
       <c r="F32" s="3">
@@ -2363,20 +2372,20 @@
         <v>4.2817640800357889E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A33" s="5">
         <v>30</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="3">
+      <c r="B33" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="5">
         <v>31</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="5">
         <v>70064.579549999995</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="5">
         <v>105</v>
       </c>
       <c r="F33" s="3">
@@ -2392,20 +2401,20 @@
         <v>4.281764080035802E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A34" s="5">
         <v>31</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="3">
+      <c r="B34" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="5">
         <v>32</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="5">
         <v>72400.065535000002</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="5">
         <v>114</v>
       </c>
       <c r="F34" s="3">
@@ -2421,20 +2430,20 @@
         <v>3.853587672032198E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A35" s="5">
         <v>32</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="3">
+      <c r="B35" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5">
         <v>33</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="5">
         <v>74735.551519999994</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="5">
         <v>209</v>
       </c>
       <c r="F35" s="3">
@@ -2450,20 +2459,20 @@
         <v>4.0676758760340118E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A36" s="5">
         <v>33</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="3">
+      <c r="B36" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="5">
         <v>34</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="5">
         <v>77071.037505</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="5">
         <v>476</v>
       </c>
       <c r="F36" s="3">
@@ -2479,20 +2488,20 @@
         <v>0.1143231009369552</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A37" s="5">
         <v>34</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="3">
+      <c r="B37" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="5">
         <v>35</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="5">
         <v>79406.523490000007</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="5">
         <v>258</v>
       </c>
       <c r="F37" s="3">
@@ -2508,20 +2517,20 @@
         <v>9.3342456944779897E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A38" s="5">
         <v>35</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="3">
+      <c r="B38" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="5">
         <v>36</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="5">
         <v>81742.009474999999</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="5">
         <v>269</v>
       </c>
       <c r="F38" s="3">
@@ -2537,20 +2546,20 @@
         <v>4.7099404880393825E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A39" s="5">
         <v>36</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="3">
+      <c r="B39" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="5">
         <v>37</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="5">
         <v>84077.495460000006</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="5">
         <v>422</v>
       </c>
       <c r="F39" s="3">
@@ -2566,20 +2575,20 @@
         <v>6.5510990424547361E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A40" s="5">
         <v>37</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="3">
+      <c r="B40" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="5">
         <v>38</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="5">
         <v>86412.981444999998</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="5">
         <v>761</v>
       </c>
       <c r="F40" s="3">
@@ -2595,20 +2604,20 @@
         <v>0.1451518023132137</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A41" s="5">
         <v>38</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="3">
+      <c r="B41" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="5">
         <v>39</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="5">
         <v>88748.467430000004</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="5">
         <v>1556</v>
       </c>
       <c r="F41" s="3">
@@ -2624,20 +2633,20 @@
         <v>0.34040024436284416</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A42" s="5">
         <v>39</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="3">
+      <c r="B42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="5">
         <v>40</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="5">
         <v>91083.953414999996</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="5">
         <v>1470</v>
       </c>
       <c r="F42" s="3">
@@ -2653,20 +2662,20 @@
         <v>3.6823171088307897E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A43" s="5">
         <v>40</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="3">
+      <c r="B43" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5">
         <v>41</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="5">
         <v>93419.439400000003</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="5">
         <v>1240</v>
       </c>
       <c r="F43" s="3">
@@ -2682,20 +2691,20 @@
         <v>9.848057384082283E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A44" s="5">
         <v>41</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="3">
+      <c r="B44" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="5">
         <v>42</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="5">
         <v>95754.925384999995</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="5">
         <v>882</v>
       </c>
       <c r="F44" s="3">
@@ -2711,20 +2720,20 @@
         <v>0.15328715406528171</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A45" s="5">
         <v>42</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="3">
+      <c r="B45" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="5">
         <v>43</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="5">
         <v>98090.411370000002</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="5">
         <v>1696</v>
       </c>
       <c r="F45" s="3">
@@ -2740,20 +2749,20 @@
         <v>0.34853559611491214</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A46" s="5">
         <v>43</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="3">
+      <c r="B46" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="5">
         <v>44</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="5">
         <v>100425.89735499999</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="5">
         <v>1858</v>
       </c>
       <c r="F46" s="3">
@@ -2769,20 +2778,20 @@
         <v>6.936457809657999E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A47" s="5">
         <v>44</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="3">
+      <c r="B47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="5">
         <v>45</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="5">
         <v>102761.38334</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="5">
         <v>1656</v>
       </c>
       <c r="F47" s="3">
@@ -2798,20 +2807,20 @@
         <v>8.6491634416722668E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A48" s="5">
         <v>45</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="3">
+      <c r="B48" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="5">
         <v>46</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="5">
         <v>105096.86932500001</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="5">
         <v>1973</v>
       </c>
       <c r="F48" s="3">
@@ -2827,20 +2836,20 @@
         <v>0.13573192133713408</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A49" s="5">
         <v>46</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="3">
+      <c r="B49" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="5">
         <v>47</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="5">
         <v>107432.35531</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="5">
         <v>1471</v>
       </c>
       <c r="F49" s="3">
@@ -2856,20 +2865,20 @@
         <v>0.21494455681779726</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A50" s="5">
         <v>47</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="3">
+      <c r="B50" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="5">
         <v>48</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="5">
         <v>109767.84129500001</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="5">
         <v>2187</v>
       </c>
       <c r="F50" s="3">
@@ -2885,20 +2894,20 @@
         <v>0.30657430813056152</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A51" s="5">
         <v>48</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="3">
+      <c r="B51" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="5">
         <v>49</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="5">
         <v>112103.32728</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="5">
         <v>1787</v>
       </c>
       <c r="F51" s="3">
@@ -2914,20 +2923,20 @@
         <v>0.17127056320143208</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A52" s="5">
         <v>49</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="3">
+      <c r="B52" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="5">
         <v>50</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="5">
         <v>114438.813265</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="5">
         <v>2346</v>
       </c>
       <c r="F52" s="3">
@@ -2943,20 +2952,20 @@
         <v>0.23935061207399985</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A53" s="5">
         <v>50</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="3">
+      <c r="B53" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="5">
         <v>51</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="5">
         <v>116774.29925</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="5">
         <v>2971</v>
       </c>
       <c r="F53" s="3">
